--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10076.12017207754</v>
+        <v>11580.30261561199</v>
       </c>
       <c r="C2">
-        <v>27811.65091790377</v>
+        <v>29584.26035707995</v>
       </c>
       <c r="D2">
-        <v>63204.31197554083</v>
+        <v>64619.69884619595</v>
       </c>
       <c r="E2">
-        <v>100982.568849053</v>
+        <v>102199.3751742635</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>91566.77868434122</v>
+        <v>122464.2955637964</v>
       </c>
       <c r="C3">
-        <v>232818.8663732686</v>
+        <v>272256.8354711671</v>
       </c>
       <c r="D3">
-        <v>338412.210825233</v>
+        <v>371596.2349588982</v>
       </c>
       <c r="E3">
-        <v>411199.3950839322</v>
+        <v>425883.3870430672</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9823.351918722006</v>
+        <v>13352.63224094648</v>
       </c>
       <c r="C4">
-        <v>25801.07998925778</v>
+        <v>30210.37693070136</v>
       </c>
       <c r="D4">
-        <v>49470.79332206396</v>
+        <v>54235.89665467993</v>
       </c>
       <c r="E4">
-        <v>69989.39968750952</v>
+        <v>72527.01113649014</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>51564.31835358255</v>
+        <v>81649.03665943464</v>
       </c>
       <c r="C6">
-        <v>92410.23844985211</v>
+        <v>117976.6774039426</v>
       </c>
       <c r="D6">
-        <v>102989.9613283158</v>
+        <v>115576.4297991594</v>
       </c>
       <c r="E6">
-        <v>92480.02948649126</v>
+        <v>96260.76143690149</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5447.790072557411</v>
+        <v>7121.848640377708</v>
       </c>
       <c r="C7">
-        <v>15173.97064725417</v>
+        <v>17438.80886210078</v>
       </c>
       <c r="D7">
-        <v>20173.92876528144</v>
+        <v>21963.0403401905</v>
       </c>
       <c r="E7">
-        <v>24032.46842626536</v>
+        <v>24878.95327818449</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>398168.2978063619</v>
+        <v>541069.3272346014</v>
       </c>
       <c r="C9">
-        <v>893084.010999167</v>
+        <v>1038937.470366691</v>
       </c>
       <c r="D9">
-        <v>1464361.658241609</v>
+        <v>1585651.351526879</v>
       </c>
       <c r="E9">
-        <v>1975771.995828311</v>
+        <v>2043954.018329535</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>509799.3983904044</v>
+        <v>558428.4323940065</v>
       </c>
       <c r="C12">
-        <v>808302.4041725744</v>
+        <v>845969.9230765784</v>
       </c>
       <c r="D12">
-        <v>839273.8608233988</v>
+        <v>853773.2215057021</v>
       </c>
       <c r="E12">
-        <v>674570.6413512344</v>
+        <v>677788.8041245657</v>
       </c>
     </row>
     <row r="13" spans="1:5">
